--- a/Spark/Data/Simulated/Bruno/model_run/results/ranking_importancia_VS_cost_SE_persist.xlsx
+++ b/Spark/Data/Simulated/Bruno/model_run/results/ranking_importancia_VS_cost_SE_persist.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">term</t>
   </si>
@@ -20,19 +20,16 @@
     <t xml:space="preserve">estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">se</t>
+    <t xml:space="preserve">conf.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conf.high</t>
   </si>
   <si>
     <t xml:space="preserve">p.value</t>
   </si>
   <si>
     <t xml:space="preserve">custo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conf.low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conf.high</t>
   </si>
   <si>
     <t xml:space="preserve">sig</t>
@@ -521,848 +518,773 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>-0.0451703696047482</v>
       </c>
       <c r="C2" t="n">
-        <v>0.044164474336335</v>
+        <v>-0.131731148700108</v>
       </c>
       <c r="D2" t="n">
+        <v>0.041390409490612</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.306413712312896</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
-        <v>-0.131732739303965</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0413920000944685</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
         <v>13</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
         <v>0.198554839404179</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0570286611952595</v>
+        <v>0.0867807173749331</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000498301918367118</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.08677866346147</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.310331015346887</v>
-      </c>
-      <c r="H3" t="s">
+        <v>0.310328961433424</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.000498301918367083</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>0.310774137250541</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0598076171261325</v>
+        <v>0.19355336168216</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000000203370566083718</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.193551207683321</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.42799706681776</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
+        <v>0.427994912818921</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.000000203370566165262</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>-0.335107386289957</v>
       </c>
       <c r="C5" t="n">
-        <v>0.039843773382305</v>
+        <v>-0.413199747127451</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000000000000000408150362816943</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.413201182119275</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.257013590460639</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
+        <v>-0.257015025452464</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
       </c>
       <c r="J5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" t="n">
         <v>0.348160360951969</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0656884266352477</v>
+        <v>0.219413410545782</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000000115689764114109</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.219411044746883</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.476909677157054</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
+        <v>0.476907311358156</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.000000115689764212945</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
       </c>
       <c r="J6" t="s">
         <v>27</v>
       </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="n">
         <v>0.0876016682149051</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0372083078648739</v>
+        <v>0.0146747248740738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.018554743625454</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0146733847997522</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.160529951630058</v>
-      </c>
-      <c r="H7" t="s">
+        <v>0.160528611555736</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0185547436254541</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
         <v>30</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
       </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
         <v>-0.0421325440812549</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0441660083769371</v>
+        <v>-0.128696329840946</v>
       </c>
       <c r="D8" t="n">
+        <v>0.0444312416784362</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.340104592485162</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
         <v>33</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.128697920500052</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.0444328323375419</v>
-      </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
         <v>0.183509519714846</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0570319899617587</v>
+        <v>0.0717288734231491</v>
       </c>
       <c r="D9" t="n">
+        <v>0.295290166006543</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.00129241182185647</v>
       </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0717268193897989</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.295292220039893</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
         <v>35</v>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>0.344915873367334</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0598100736440866</v>
+        <v>0.227690283112236</v>
       </c>
       <c r="D10" t="n">
+        <v>0.462141463622432</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.00000000807656741486085</v>
       </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.227688129024925</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.462143617709744</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>-0.34588367432304</v>
       </c>
       <c r="C11" t="n">
-        <v>0.039845411984625</v>
+        <v>-0.423979246762065</v>
       </c>
       <c r="D11" t="n">
+        <v>-0.267788101884014</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.423980681812905</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.267786666833175</v>
-      </c>
-      <c r="H11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" t="n">
         <v>0.35397960406103</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0656911368480847</v>
+        <v>0.225227341735292</v>
       </c>
       <c r="D12" t="n">
+        <v>0.482731866386768</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.000000071030637371905</v>
       </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.225224975838784</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.482734232283276</v>
-      </c>
-      <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
       </c>
       <c r="J12" t="s">
         <v>27</v>
       </c>
-      <c r="K12" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" t="n">
         <v>0.094098708517689</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0372097328336388</v>
+        <v>0.0211689722893995</v>
       </c>
       <c r="D13" t="n">
+        <v>0.167028444745978</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.011442925108335</v>
       </c>
-      <c r="E13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.021167632163757</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.167029784871621</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
         <v>30</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
       </c>
       <c r="J13" t="s">
         <v>31</v>
       </c>
-      <c r="K13" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
         <v>-0.0431518380996558</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0441730875275442</v>
+        <v>-0.129729498739578</v>
       </c>
       <c r="D14" t="n">
+        <v>0.0434258225402663</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.32862820159552</v>
       </c>
-      <c r="E14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.129731089653642</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0434274134543308</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
         <v>13</v>
       </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
       <c r="J14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="n">
         <v>0.0843803681609692</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0570425380262129</v>
+        <v>-0.0274209519571646</v>
       </c>
       <c r="D15" t="n">
+        <v>0.196181688279103</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.139072603108951</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
         <v>39</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.0274230063704081</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.196183742692347</v>
-      </c>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>0.395815422676028</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0598172814017528</v>
+        <v>0.278575705475495</v>
       </c>
       <c r="D16" t="n">
+        <v>0.513055139876562</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.0000000000366375818572351</v>
       </c>
-      <c r="E16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.278573551128593</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.513057294223464</v>
-      </c>
-      <c r="H16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="n">
         <v>-0.319261914244702</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0398476183074763</v>
+        <v>-0.397361810997054</v>
       </c>
       <c r="D17" t="n">
+        <v>-0.24116201749235</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.00000000000000111022302462516</v>
       </c>
-      <c r="E17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.397363246127356</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.241160582362048</v>
-      </c>
-      <c r="H17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="n">
         <v>0.349665452506769</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0656968110049302</v>
+        <v>0.220902069037971</v>
       </c>
       <c r="D18" t="n">
+        <v>0.478428835975567</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.00000010240069103773</v>
       </c>
-      <c r="E18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.220899702937106</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.478431202076432</v>
-      </c>
-      <c r="H18" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
       </c>
       <c r="J18" t="s">
         <v>27</v>
       </c>
-      <c r="K18" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" t="n">
         <v>0.095804427891325</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0372132841617939</v>
+        <v>0.0228677311877542</v>
       </c>
       <c r="D19" t="n">
+        <v>0.168741124594896</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.0100394227515703</v>
       </c>
-      <c r="E19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.022866390934209</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.168742464848441</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
         <v>30</v>
       </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
       <c r="J19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" t="n">
         <v>-0.0328399662532347</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0442780934461138</v>
+        <v>-0.119623434711717</v>
       </c>
       <c r="D20" t="n">
+        <v>0.0539435022052473</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.458284115714793</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" t="s">
         <v>44</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.119625029407618</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.0539450969011483</v>
-      </c>
-      <c r="H20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="n">
         <v>-0.133838449562925</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0571812950007942</v>
+        <v>-0.245911728353841</v>
       </c>
       <c r="D21" t="n">
+        <v>-0.0217651707720077</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.0192528624568924</v>
       </c>
-      <c r="E21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.245913787764481</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.0217631113613679</v>
-      </c>
-      <c r="H21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
+      <c r="F21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
         <v>0.299160829586298</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0599556893029094</v>
+        <v>0.181649837884323</v>
       </c>
       <c r="D22" t="n">
+        <v>0.416671821288274</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.000000604735176157334</v>
       </c>
-      <c r="E22" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.181647678552596</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.416673980620001</v>
-      </c>
-      <c r="H22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
+      <c r="F22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
       </c>
       <c r="J22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
         <v>-0.280281172062501</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0399388778663943</v>
+        <v>-0.358559934263578</v>
       </c>
       <c r="D23" t="n">
+        <v>-0.202002409861424</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.00000000000225464091840877</v>
       </c>
-      <c r="E23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.358561372680634</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.202000971444368</v>
-      </c>
-      <c r="H23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
+      <c r="F23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="n">
         <v>0.308934381337527</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0658432210815683</v>
+        <v>0.179884039391545</v>
       </c>
       <c r="D24" t="n">
+        <v>0.43798472328351</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.00000270587549633383</v>
       </c>
-      <c r="E24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.179881668017653</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.437987094657401</v>
-      </c>
-      <c r="H24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
+      <c r="F24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>27</v>
-      </c>
-      <c r="K24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n">
         <v>0.113355902457046</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0372960163362218</v>
+        <v>0.0402570536712337</v>
       </c>
       <c r="D25" t="n">
+        <v>0.186454751242858</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.00237083849753339</v>
       </c>
-      <c r="E25" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.0402557104380512</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.186456094476041</v>
-      </c>
-      <c r="H25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>30</v>
       </c>
       <c r="J25" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
